--- a/XLSX_DATA/RAW_DATA/NPL_raw_data.xlsx
+++ b/XLSX_DATA/RAW_DATA/NPL_raw_data.xlsx
@@ -449,12 +449,12 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>gini</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>log_gdp_pc</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>gini</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -503,10 +503,10 @@
         <v>477.741099613336</v>
       </c>
       <c r="G2" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="H2" t="n">
         <v>6.169068953147444</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35.2</v>
       </c>
       <c r="I2" t="n">
         <v>21.2738679137675</v>
@@ -545,10 +545,10 @@
       <c r="F3" t="n">
         <v>492.212428031946</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="n">
         <v>6.1989103876015</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
         <v>21.4930517891794</v>
       </c>
@@ -584,10 +584,10 @@
       <c r="F4" t="n">
         <v>506.426874424217</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
         <v>6.227379938979918</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
         <v>21.4004342044754</v>
       </c>
@@ -623,10 +623,10 @@
       <c r="F5" t="n">
         <v>511.54871132025</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
         <v>6.237442813155027</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
         <v>21.0759693529891</v>
       </c>
@@ -664,10 +664,10 @@
       <c r="F6" t="n">
         <v>524.27256909301</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="n">
         <v>6.26201171910434</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
         <v>20.4411231566268</v>
       </c>
@@ -705,10 +705,10 @@
       <c r="F7" t="n">
         <v>547.221082273632</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="n">
         <v>6.304852893113016</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
         <v>20.7355700311999</v>
       </c>
@@ -746,10 +746,10 @@
       <c r="F8" t="n">
         <v>564.28622920391</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="n">
         <v>6.335561621352696</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
         <v>16.6609082977555</v>
       </c>
@@ -787,10 +787,10 @@
       <c r="F9" t="n">
         <v>556.438454538796</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="n">
         <v>6.32155657077898</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
         <v>16.9468247421334</v>
       </c>
@@ -829,10 +829,10 @@
         <v>570.28967363428</v>
       </c>
       <c r="G10" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="H10" t="n">
         <v>6.346144431097422</v>
-      </c>
-      <c r="H10" t="n">
-        <v>43.8</v>
       </c>
       <c r="I10" t="n">
         <v>16.9713000603375</v>
@@ -869,10 +869,10 @@
       <c r="F11" t="n">
         <v>589.46992868617</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="n">
         <v>6.379223707117632</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
         <v>16.6573202744672</v>
       </c>
@@ -910,10 +910,10 @@
       <c r="F12" t="n">
         <v>603.190108570995</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="n">
         <v>6.402232418301659</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
         <v>16.4670892346949</v>
       </c>
@@ -951,10 +951,10 @@
       <c r="F13" t="n">
         <v>617.477638588722</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="n">
         <v>6.425642855034646</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
         <v>16.0679668054868</v>
       </c>
@@ -992,10 +992,10 @@
       <c r="F14" t="n">
         <v>633.226129136597</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="n">
         <v>6.450827592374355</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
         <v>15.873140183038</v>
       </c>
@@ -1033,10 +1033,10 @@
       <c r="F15" t="n">
         <v>666.865095417138</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="n">
         <v>6.502587769712752</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
         <v>16.049986636556</v>
       </c>
@@ -1074,10 +1074,10 @@
       <c r="F16" t="n">
         <v>692.400000816919</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="n">
         <v>6.540163824481891</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
         <v>15.0668034711092</v>
       </c>
@@ -1116,10 +1116,10 @@
         <v>721.265221364302</v>
       </c>
       <c r="G17" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="H17" t="n">
         <v>6.581006921744232</v>
-      </c>
-      <c r="H17" t="n">
-        <v>32.8</v>
       </c>
       <c r="I17" t="n">
         <v>14.2007622567226</v>
@@ -1158,10 +1158,10 @@
       <c r="F18" t="n">
         <v>742.617252662576</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="n">
         <v>6.610180774253302</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
         <v>13.393470598846</v>
       </c>
@@ -1199,10 +1199,10 @@
       <c r="F19" t="n">
         <v>775.310578479839</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="n">
         <v>6.653263695501543</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
         <v>13.9771618084251</v>
       </c>
@@ -1240,10 +1240,10 @@
       <c r="F20" t="n">
         <v>801.039060847856</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="n">
         <v>6.685909710982821</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
         <v>13.7983375627601</v>
       </c>
@@ -1281,10 +1281,10 @@
       <c r="F21" t="n">
         <v>846.665541773599</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="n">
         <v>6.741305742729731</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
         <v>13.5645652301586</v>
       </c>
@@ -1322,10 +1322,10 @@
       <c r="F22" t="n">
         <v>875.543635474862</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="n">
         <v>6.77484499111767</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
         <v>13.1616546296789</v>
       </c>
@@ -1363,10 +1363,10 @@
       <c r="F23" t="n">
         <v>875.188943730855</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="n">
         <v>6.774439798739264</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
         <v>12.6554177701811</v>
       </c>
@@ -1404,10 +1404,10 @@
       <c r="F24" t="n">
         <v>951.8572985636411</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="n">
         <v>6.858415127089003</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
         <v>12.8625858899927</v>
       </c>
@@ -1443,10 +1443,10 @@
       <c r="F25" t="n">
         <v>1021.91492204011</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="n">
         <v>6.929433520762369</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
         <v>13.2006396343014</v>
       </c>
@@ -1484,10 +1484,10 @@
       <c r="F26" t="n">
         <v>1077.11796498188</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="n">
         <v>6.982044202246393</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
         <v>13.0106754142894</v>
       </c>
@@ -1525,10 +1525,10 @@
       <c r="F27" t="n">
         <v>1031.53618783934</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="n">
         <v>6.938804414629165</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
         <v>12.047319925355</v>
       </c>
@@ -1566,10 +1566,10 @@
       <c r="F28" t="n">
         <v>1062.7888430629</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="n">
         <v>6.968651716147926</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
         <v>11.7920425516798</v>
       </c>
@@ -1608,10 +1608,10 @@
         <v>1113.55462341223</v>
       </c>
       <c r="G29" t="n">
+        <v>30</v>
+      </c>
+      <c r="H29" t="n">
         <v>7.0153125410957</v>
-      </c>
-      <c r="H29" t="n">
-        <v>30</v>
       </c>
       <c r="I29" t="n">
         <v>12.1812284731342</v>
@@ -1650,10 +1650,10 @@
       <c r="F30" t="n">
         <v>1136.42769313825</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="n">
         <v>7.035645018864956</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
         <v>11.9717042539851</v>
       </c>
@@ -1691,10 +1691,10 @@
       <c r="F31" t="n">
         <v>1179.81272768386</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="n">
         <v>7.073110999512022</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
         <v>11.4245020172191</v>
       </c>

--- a/XLSX_DATA/RAW_DATA/NPL_raw_data.xlsx
+++ b/XLSX_DATA/RAW_DATA/NPL_raw_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:P32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,6 +482,21 @@
           <t>palma_ratio</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>va_score</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>cc_score</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ge_score</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -521,8 +536,11 @@
         <v>23.0157968547751</v>
       </c>
       <c r="M2" t="n">
-        <v>3.671564390665514</v>
-      </c>
+        <v>4.358999037536092</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -562,8 +580,11 @@
         <v>24.1000758705435</v>
       </c>
       <c r="M3" t="n">
-        <v>3.595076400679117</v>
-      </c>
+        <v>4.538537549407114</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -605,7 +626,16 @@
         <v>25.2906817030471</v>
       </c>
       <c r="M4" t="n">
-        <v>3.521267723102585</v>
+        <v>4.465686274509804</v>
+      </c>
+      <c r="N4" t="n">
+        <v>49.95</v>
+      </c>
+      <c r="O4" t="n">
+        <v>37.26</v>
+      </c>
+      <c r="P4" t="n">
+        <v>35.99</v>
       </c>
     </row>
     <row r="5">
@@ -646,8 +676,11 @@
         <v>26.5867669012845</v>
       </c>
       <c r="M5" t="n">
-        <v>3.904424778761062</v>
-      </c>
+        <v>4.405458089668616</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -687,7 +720,16 @@
         <v>27.9874840142543</v>
       </c>
       <c r="M6" t="n">
-        <v>4.308630393996247</v>
+        <v>4.326254826254826</v>
+      </c>
+      <c r="N6" t="n">
+        <v>48.33</v>
+      </c>
+      <c r="O6" t="n">
+        <v>37.21</v>
+      </c>
+      <c r="P6" t="n">
+        <v>35.81</v>
       </c>
     </row>
     <row r="7">
@@ -730,8 +772,11 @@
         <v>29.4919855909549</v>
       </c>
       <c r="M7" t="n">
-        <v>4.199443413729128</v>
-      </c>
+        <v>4.302123552123552</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -773,7 +818,16 @@
         <v>31.0994241803849</v>
       </c>
       <c r="M8" t="n">
-        <v>4.054644808743169</v>
+        <v>4.251681075888569</v>
+      </c>
+      <c r="N8" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="O8" t="n">
+        <v>37.07</v>
+      </c>
+      <c r="P8" t="n">
+        <v>35.87</v>
       </c>
     </row>
     <row r="9">
@@ -816,8 +870,11 @@
         <v>32.808952331543</v>
       </c>
       <c r="M9" t="n">
-        <v>3.902678571428571</v>
-      </c>
+        <v>4.191793893129771</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -859,7 +916,16 @@
         <v>35.0358944291182</v>
       </c>
       <c r="M10" t="n">
-        <v>4.085793357933579</v>
+        <v>4.208453410182517</v>
+      </c>
+      <c r="N10" t="n">
+        <v>40.12</v>
+      </c>
+      <c r="O10" t="n">
+        <v>37.29</v>
+      </c>
+      <c r="P10" t="n">
+        <v>30.98</v>
       </c>
     </row>
     <row r="11">
@@ -902,7 +968,16 @@
         <v>38.045308394296</v>
       </c>
       <c r="M11" t="n">
-        <v>4.301724137931034</v>
+        <v>4.264849074975658</v>
+      </c>
+      <c r="N11" t="n">
+        <v>47.09</v>
+      </c>
+      <c r="O11" t="n">
+        <v>40.94</v>
+      </c>
+      <c r="P11" t="n">
+        <v>30.8</v>
       </c>
     </row>
     <row r="12">
@@ -943,7 +1018,16 @@
         <v>41.6109470808194</v>
       </c>
       <c r="M12" t="n">
-        <v>4.405063291139241</v>
+        <v>4.212003872216844</v>
+      </c>
+      <c r="N12" t="n">
+        <v>39.87</v>
+      </c>
+      <c r="O12" t="n">
+        <v>29.16</v>
+      </c>
+      <c r="P12" t="n">
+        <v>37.39</v>
       </c>
     </row>
     <row r="13">
@@ -986,7 +1070,16 @@
         <v>45.5065633424317</v>
       </c>
       <c r="M13" t="n">
-        <v>4.669322709163348</v>
+        <v>4.192642787996127</v>
+      </c>
+      <c r="N13" t="n">
+        <v>39.34</v>
+      </c>
+      <c r="O13" t="n">
+        <v>30.19</v>
+      </c>
+      <c r="P13" t="n">
+        <v>33.43</v>
       </c>
     </row>
     <row r="14">
@@ -1029,7 +1122,16 @@
         <v>49.5059100328759</v>
       </c>
       <c r="M14" t="n">
-        <v>4.372115384615385</v>
+        <v>4.203307392996109</v>
+      </c>
+      <c r="N14" t="n">
+        <v>45.57</v>
+      </c>
+      <c r="O14" t="n">
+        <v>32.97</v>
+      </c>
+      <c r="P14" t="n">
+        <v>31.25</v>
       </c>
     </row>
     <row r="15">
@@ -1072,7 +1174,16 @@
         <v>53.3827400058951</v>
       </c>
       <c r="M15" t="n">
-        <v>4.113805970149254</v>
+        <v>4.242632612966601</v>
+      </c>
+      <c r="N15" t="n">
+        <v>50.37</v>
+      </c>
+      <c r="O15" t="n">
+        <v>32</v>
+      </c>
+      <c r="P15" t="n">
+        <v>32.93</v>
       </c>
     </row>
     <row r="16">
@@ -1115,7 +1226,16 @@
         <v>56.9108061152324</v>
       </c>
       <c r="M16" t="n">
-        <v>3.861730597680642</v>
+        <v>4.038973384030419</v>
+      </c>
+      <c r="N16" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="O16" t="n">
+        <v>30.38</v>
+      </c>
+      <c r="P16" t="n">
+        <v>31.58</v>
       </c>
     </row>
     <row r="17">
@@ -1158,7 +1278,16 @@
         <v>59.8638612146309</v>
       </c>
       <c r="M17" t="n">
-        <v>3.747156605424322</v>
+        <v>3.970809792843691</v>
+      </c>
+      <c r="N17" t="n">
+        <v>49.27</v>
+      </c>
+      <c r="O17" t="n">
+        <v>32.52</v>
+      </c>
+      <c r="P17" t="n">
+        <v>36.03</v>
       </c>
     </row>
     <row r="18">
@@ -1201,7 +1330,16 @@
         <v>62.0156581578338</v>
       </c>
       <c r="M18" t="n">
-        <v>3.792035398230088</v>
+        <v>4.072115384615385</v>
+      </c>
+      <c r="N18" t="n">
+        <v>48.43</v>
+      </c>
+      <c r="O18" t="n">
+        <v>33.13</v>
+      </c>
+      <c r="P18" t="n">
+        <v>37.87</v>
       </c>
     </row>
     <row r="19">
@@ -1244,7 +1382,16 @@
         <v>63.139949798584</v>
       </c>
       <c r="M19" t="n">
-        <v>3.787905346187555</v>
+        <v>3.982024597918638</v>
+      </c>
+      <c r="N19" t="n">
+        <v>49.39</v>
+      </c>
+      <c r="O19" t="n">
+        <v>31.02</v>
+      </c>
+      <c r="P19" t="n">
+        <v>35.86</v>
       </c>
     </row>
     <row r="20">
@@ -1287,7 +1434,16 @@
         <v>63.6558406194333</v>
       </c>
       <c r="M20" t="n">
-        <v>3.724498692240628</v>
+        <v>3.965094339622642</v>
+      </c>
+      <c r="N20" t="n">
+        <v>48.33</v>
+      </c>
+      <c r="O20" t="n">
+        <v>28.15</v>
+      </c>
+      <c r="P20" t="n">
+        <v>29.77</v>
       </c>
     </row>
     <row r="21">
@@ -1330,7 +1486,16 @@
         <v>64.13145701560479</v>
       </c>
       <c r="M21" t="n">
-        <v>3.649653979238754</v>
+        <v>3.935272045028142</v>
+      </c>
+      <c r="N21" t="n">
+        <v>50.31</v>
+      </c>
+      <c r="O21" t="n">
+        <v>29.27</v>
+      </c>
+      <c r="P21" t="n">
+        <v>30.89</v>
       </c>
     </row>
     <row r="22">
@@ -1373,7 +1538,16 @@
         <v>64.5640847098488</v>
       </c>
       <c r="M22" t="n">
-        <v>3.807929515418502</v>
+        <v>3.882899628252788</v>
+      </c>
+      <c r="N22" t="n">
+        <v>51.24</v>
+      </c>
+      <c r="O22" t="n">
+        <v>30.79</v>
+      </c>
+      <c r="P22" t="n">
+        <v>33.93</v>
       </c>
     </row>
     <row r="23">
@@ -1416,7 +1590,16 @@
         <v>64.9510094249155</v>
       </c>
       <c r="M23" t="n">
-        <v>3.923487544483986</v>
+        <v>3.793418647166362</v>
+      </c>
+      <c r="N23" t="n">
+        <v>51.16</v>
+      </c>
+      <c r="O23" t="n">
+        <v>31.04</v>
+      </c>
+      <c r="P23" t="n">
+        <v>28.72</v>
       </c>
     </row>
     <row r="24">
@@ -1459,7 +1642,16 @@
         <v>65.28951688355529</v>
       </c>
       <c r="M24" t="n">
-        <v>3.836411609498681</v>
+        <v>3.779398359161349</v>
+      </c>
+      <c r="N24" t="n">
+        <v>52.58</v>
+      </c>
+      <c r="O24" t="n">
+        <v>30.73</v>
+      </c>
+      <c r="P24" t="n">
+        <v>32.25</v>
       </c>
     </row>
     <row r="25">
@@ -1502,7 +1694,16 @@
         <v>65.57689280851839</v>
       </c>
       <c r="M25" t="n">
-        <v>3.767218831734961</v>
+        <v>3.783759124087591</v>
+      </c>
+      <c r="N25" t="n">
+        <v>53.63</v>
+      </c>
+      <c r="O25" t="n">
+        <v>32.04</v>
+      </c>
+      <c r="P25" t="n">
+        <v>33.3</v>
       </c>
     </row>
     <row r="26">
@@ -1543,7 +1744,16 @@
         <v>65.81042292255511</v>
       </c>
       <c r="M26" t="n">
-        <v>3.700086430423509</v>
+        <v>3.783759124087591</v>
+      </c>
+      <c r="N26" t="n">
+        <v>54.71</v>
+      </c>
+      <c r="O26" t="n">
+        <v>32.91</v>
+      </c>
+      <c r="P26" t="n">
+        <v>33.56</v>
       </c>
     </row>
     <row r="27">
@@ -1586,7 +1796,16 @@
         <v>65.9873929484157</v>
       </c>
       <c r="M27" t="n">
-        <v>3.700086430423509</v>
+        <v>3.783759124087591</v>
+      </c>
+      <c r="N27" t="n">
+        <v>53.78</v>
+      </c>
+      <c r="O27" t="n">
+        <v>32.94</v>
+      </c>
+      <c r="P27" t="n">
+        <v>29.73</v>
       </c>
     </row>
     <row r="28">
@@ -1629,7 +1848,16 @@
         <v>66.10508860885049</v>
       </c>
       <c r="M28" t="n">
-        <v>3.700086430423509</v>
+        <v>3.783759124087591</v>
+      </c>
+      <c r="N28" t="n">
+        <v>54.55</v>
+      </c>
+      <c r="O28" t="n">
+        <v>33.66</v>
+      </c>
+      <c r="P28" t="n">
+        <v>31.38</v>
       </c>
     </row>
     <row r="29">
@@ -1672,7 +1900,16 @@
         <v>66.144235274522</v>
       </c>
       <c r="M29" t="n">
-        <v>3.700086430423509</v>
+        <v>3.783759124087591</v>
+      </c>
+      <c r="N29" t="n">
+        <v>54.32</v>
+      </c>
+      <c r="O29" t="n">
+        <v>35.21</v>
+      </c>
+      <c r="P29" t="n">
+        <v>32.94</v>
       </c>
     </row>
     <row r="30">
@@ -1715,7 +1952,16 @@
         <v>66.2992968721053</v>
       </c>
       <c r="M30" t="n">
-        <v>3.700086430423509</v>
+        <v>3.783759124087591</v>
+      </c>
+      <c r="N30" t="n">
+        <v>55.12</v>
+      </c>
+      <c r="O30" t="n">
+        <v>34.66</v>
+      </c>
+      <c r="P30" t="n">
+        <v>32.78</v>
       </c>
     </row>
     <row r="31">
@@ -1758,7 +2004,16 @@
         <v>66.5432933453944</v>
       </c>
       <c r="M31" t="n">
-        <v>3.700086430423509</v>
+        <v>3.783759124087591</v>
+      </c>
+      <c r="N31" t="n">
+        <v>55.92</v>
+      </c>
+      <c r="O31" t="n">
+        <v>35.12</v>
+      </c>
+      <c r="P31" t="n">
+        <v>34.93</v>
       </c>
     </row>
     <row r="32">
@@ -1801,7 +2056,16 @@
         <v>66.77234316302901</v>
       </c>
       <c r="M32" t="n">
-        <v>3.700086430423509</v>
+        <v>3.783759124087591</v>
+      </c>
+      <c r="N32" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="O32" t="n">
+        <v>35.05</v>
+      </c>
+      <c r="P32" t="n">
+        <v>34.14</v>
       </c>
     </row>
   </sheetData>
